--- a/artfynd/A 24615-2026 artfynd.xlsx
+++ b/artfynd/A 24615-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,6 +1158,675 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134178474</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99200</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>781969</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7295552</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134178480</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106291</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>781874</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7295524</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134178478</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80478</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>781853</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7295531</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134178477</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106291</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>782007</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7295501</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>100tal</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134178476</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106291</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>782015</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7295517</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>100tal</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134178479</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80473</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>781851</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7295532</v>
+      </c>
+      <c r="S12" t="n">
+        <v>13</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24615-2026 artfynd.xlsx
+++ b/artfynd/A 24615-2026 artfynd.xlsx
@@ -1284,10 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134178480</v>
+        <v>134178478</v>
       </c>
       <c r="B8" t="n">
-        <v>106291</v>
+        <v>80478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,21 +1295,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781874</v>
+        <v>781853</v>
       </c>
       <c r="R8" t="n">
-        <v>7295524</v>
+        <v>7295531</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,32 +1391,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134178478</v>
+        <v>134178479</v>
       </c>
       <c r="B9" t="n">
-        <v>80478</v>
+        <v>80473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,13 +1426,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781853</v>
+        <v>781851</v>
       </c>
       <c r="R9" t="n">
-        <v>7295531</v>
+        <v>7295532</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,7 +1498,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134178477</v>
+        <v>134178480</v>
       </c>
       <c r="B10" t="n">
         <v>106291</v>
@@ -1526,20 +1526,36 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långstrandberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782007</v>
+        <v>781874</v>
       </c>
       <c r="R10" t="n">
-        <v>7295501</v>
+        <v>7295524</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1568,7 +1584,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1578,12 +1594,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:57</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>100tal</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,6 +1603,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1610,7 +1622,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134178476</v>
+        <v>134178477</v>
       </c>
       <c r="B11" t="n">
         <v>106291</v>
@@ -1638,17 +1650,33 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långstrandberget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782015</v>
+        <v>782007</v>
       </c>
       <c r="R11" t="n">
-        <v>7295517</v>
+        <v>7295501</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1680,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1690,12 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>100tal</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1704,6 +1727,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1722,48 +1746,64 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134178479</v>
+        <v>134178476</v>
       </c>
       <c r="B12" t="n">
-        <v>80473</v>
+        <v>106291</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långstrandberget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781851</v>
+        <v>782015</v>
       </c>
       <c r="R12" t="n">
-        <v>7295532</v>
+        <v>7295517</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1792,7 +1832,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1802,7 +1842,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1811,6 +1851,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24615-2026 artfynd.xlsx
+++ b/artfynd/A 24615-2026 artfynd.xlsx
@@ -1501,7 +1501,7 @@
         <v>134178480</v>
       </c>
       <c r="B10" t="n">
-        <v>106291</v>
+        <v>106292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>134178477</v>
       </c>
       <c r="B11" t="n">
-        <v>106291</v>
+        <v>106292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>134178476</v>
       </c>
       <c r="B12" t="n">
-        <v>106291</v>
+        <v>106292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2026 artfynd.xlsx
+++ b/artfynd/A 24615-2026 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>134178474</v>
       </c>
       <c r="B7" t="n">
-        <v>99200</v>
+        <v>99202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>134178478</v>
       </c>
       <c r="B8" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>134178479</v>
       </c>
       <c r="B9" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>134178480</v>
       </c>
       <c r="B10" t="n">
-        <v>106292</v>
+        <v>106294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>134178477</v>
       </c>
       <c r="B11" t="n">
-        <v>106292</v>
+        <v>106294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>134178476</v>
       </c>
       <c r="B12" t="n">
-        <v>106292</v>
+        <v>106294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2026 artfynd.xlsx
+++ b/artfynd/A 24615-2026 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>134178474</v>
       </c>
       <c r="B7" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>134178478</v>
       </c>
       <c r="B8" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>134178479</v>
       </c>
       <c r="B9" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>134178480</v>
       </c>
       <c r="B10" t="n">
-        <v>106295</v>
+        <v>106302</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>134178477</v>
       </c>
       <c r="B11" t="n">
-        <v>106295</v>
+        <v>106302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>134178476</v>
       </c>
       <c r="B12" t="n">
-        <v>106295</v>
+        <v>106302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2026 artfynd.xlsx
+++ b/artfynd/A 24615-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127775015</v>
+        <v>127775009</v>
       </c>
       <c r="B2" t="n">
-        <v>80223</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781858</v>
+        <v>781837</v>
       </c>
       <c r="R2" t="n">
-        <v>7295536</v>
+        <v>7295531</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127775000</v>
+        <v>127775004</v>
       </c>
       <c r="B3" t="n">
-        <v>80217</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781856</v>
+        <v>781933</v>
       </c>
       <c r="R3" t="n">
-        <v>7295530</v>
+        <v>7295515</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127775004</v>
+        <v>134178479</v>
       </c>
       <c r="B4" t="n">
-        <v>80188</v>
+        <v>80488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,17 +900,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstrandberget, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781933</v>
+        <v>781851</v>
       </c>
       <c r="R4" t="n">
-        <v>7295515</v>
+        <v>7295532</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,12 +934,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,22 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127774997</v>
+        <v>127775000</v>
       </c>
       <c r="B5" t="n">
-        <v>105594</v>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781857</v>
+        <v>781856</v>
       </c>
       <c r="R5" t="n">
-        <v>7295534</v>
+        <v>7295530</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1076,7 @@
         <v>127775001</v>
       </c>
       <c r="B6" t="n">
-        <v>80217</v>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134178474</v>
+        <v>134178478</v>
       </c>
       <c r="B7" t="n">
-        <v>99210</v>
+        <v>80493</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,50 +1181,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långstrandberget, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781969</v>
+        <v>781853</v>
       </c>
       <c r="R7" t="n">
-        <v>7295552</v>
+        <v>7295531</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1246,7 +1240,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1256,7 +1250,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,7 +1259,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1284,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134178478</v>
+        <v>127775015</v>
       </c>
       <c r="B8" t="n">
-        <v>80486</v>
+        <v>80467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,37 +1288,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långstrandberget, Nb</t>
+          <t>Maran/Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781853</v>
+        <v>781858</v>
       </c>
       <c r="R8" t="n">
-        <v>7295531</v>
+        <v>7295536</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1349,22 +1342,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:34</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:34</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,60 +1362,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134178479</v>
+        <v>127774997</v>
       </c>
       <c r="B9" t="n">
-        <v>80481</v>
+        <v>106229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långstrandberget, Nb</t>
+          <t>Maran/Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781851</v>
+        <v>781857</v>
       </c>
       <c r="R9" t="n">
-        <v>7295532</v>
+        <v>7295534</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,22 +1439,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,22 +1459,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134178480</v>
+        <v>134178476</v>
       </c>
       <c r="B10" t="n">
-        <v>106302</v>
+        <v>106309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1528,7 +1501,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1549,13 +1522,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781874</v>
+        <v>782015</v>
       </c>
       <c r="R10" t="n">
-        <v>7295524</v>
+        <v>7295517</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1584,7 +1557,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1594,7 +1567,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,7 +1598,7 @@
         <v>134178477</v>
       </c>
       <c r="B11" t="n">
-        <v>106302</v>
+        <v>106309</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134178476</v>
+        <v>134178480</v>
       </c>
       <c r="B12" t="n">
-        <v>106302</v>
+        <v>106309</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,7 +1749,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1797,13 +1770,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>782015</v>
+        <v>781874</v>
       </c>
       <c r="R12" t="n">
-        <v>7295517</v>
+        <v>7295524</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1832,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1842,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,6 +1840,227 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127775003</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Maran/Täxtberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>781828</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7295541</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134178474</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>781969</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7295552</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24615-2026 artfynd.xlsx
+++ b/artfynd/A 24615-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127774997</v>
+        <v>134178475</v>
       </c>
       <c r="B9" t="n">
-        <v>106229</v>
+        <v>57165</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,37 +1385,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>102613</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstrandberget, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781857</v>
+        <v>781987</v>
       </c>
       <c r="R9" t="n">
-        <v>7295534</v>
+        <v>7295546</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,12 +1439,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flög</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1459,22 +1474,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134178476</v>
+        <v>127774997</v>
       </c>
       <c r="B10" t="n">
-        <v>106309</v>
+        <v>106229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,36 +1514,20 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långstrandberget, Nb</t>
+          <t>Maran/Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782015</v>
+        <v>781857</v>
       </c>
       <c r="R10" t="n">
-        <v>7295517</v>
+        <v>7295534</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1552,22 +1551,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:44</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:44</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1576,26 +1565,25 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134178477</v>
+        <v>134178476</v>
       </c>
       <c r="B11" t="n">
         <v>106309</v>
@@ -1646,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782007</v>
+        <v>782015</v>
       </c>
       <c r="R11" t="n">
-        <v>7295501</v>
+        <v>7295517</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1681,7 +1669,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1691,7 +1679,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,7 +1707,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134178480</v>
+        <v>134178477</v>
       </c>
       <c r="B12" t="n">
         <v>106309</v>
@@ -1749,7 +1737,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1770,13 +1758,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781874</v>
+        <v>782007</v>
       </c>
       <c r="R12" t="n">
-        <v>7295524</v>
+        <v>7295501</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1805,7 +1793,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1803,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127775003</v>
+        <v>134178480</v>
       </c>
       <c r="B13" t="n">
-        <v>97983</v>
+        <v>106309</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1854,37 +1842,53 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstrandberget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781828</v>
+        <v>781874</v>
       </c>
       <c r="R13" t="n">
-        <v>7295541</v>
+        <v>7295524</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1908,12 +1912,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1922,28 +1936,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134178474</v>
+        <v>127775003</v>
       </c>
       <c r="B14" t="n">
-        <v>99217</v>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,53 +1966,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långstrandberget, Nb</t>
+          <t>Maran/Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781969</v>
+        <v>781828</v>
       </c>
       <c r="R14" t="n">
-        <v>7295552</v>
+        <v>7295541</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2021,22 +2020,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2045,22 +2034,145 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134178474</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>781969</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7295552</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Linda-Marie Grahn</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Linda-Marie Grahn</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24615-2026 artfynd.xlsx
+++ b/artfynd/A 24615-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127775009</v>
+        <v>135266989</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>83222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781837</v>
+        <v>781856</v>
       </c>
       <c r="R2" t="n">
-        <v>7295531</v>
+        <v>7295511</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre gran med grenar hängande längs  stan, delvis grånade grenar med lav.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,48 +787,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127775004</v>
+        <v>135266986</v>
       </c>
       <c r="B3" t="n">
-        <v>80432</v>
+        <v>97308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781933</v>
+        <v>781866</v>
       </c>
       <c r="R3" t="n">
-        <v>7295515</v>
+        <v>7295532</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,48 +894,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134178479</v>
+        <v>127775009</v>
       </c>
       <c r="B4" t="n">
-        <v>80488</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långstrandberget, Nb</t>
+          <t>Maran/Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781851</v>
+        <v>781837</v>
       </c>
       <c r="R4" t="n">
-        <v>7295532</v>
+        <v>7295531</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,22 +959,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,60 +979,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127775000</v>
+        <v>135266990</v>
       </c>
       <c r="B5" t="n">
-        <v>80461</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781856</v>
+        <v>781844</v>
       </c>
       <c r="R5" t="n">
-        <v>7295530</v>
+        <v>7295502</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1041,12 +1056,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,32 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127775001</v>
+        <v>127775004</v>
       </c>
       <c r="B6" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781881</v>
+        <v>781933</v>
       </c>
       <c r="R6" t="n">
-        <v>7295532</v>
+        <v>7295515</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,32 +1195,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134178478</v>
+        <v>134178479</v>
       </c>
       <c r="B7" t="n">
-        <v>80493</v>
+        <v>80488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781853</v>
+        <v>781851</v>
       </c>
       <c r="R7" t="n">
-        <v>7295531</v>
+        <v>7295532</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1240,7 +1265,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1250,7 +1275,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,48 +1302,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127775015</v>
+        <v>135266974</v>
       </c>
       <c r="B8" t="n">
-        <v>80467</v>
+        <v>80488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781858</v>
+        <v>781996</v>
       </c>
       <c r="R8" t="n">
-        <v>7295536</v>
+        <v>7295563</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1367,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,48 +1409,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134178475</v>
+        <v>135266983</v>
       </c>
       <c r="B9" t="n">
-        <v>57165</v>
+        <v>80488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102613</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långstrandberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781987</v>
+        <v>781931</v>
       </c>
       <c r="R9" t="n">
-        <v>7295546</v>
+        <v>7295507</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1444,7 +1479,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1454,12 +1489,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flög</t>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,60 +1509,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127774997</v>
+        <v>135266984</v>
       </c>
       <c r="B10" t="n">
-        <v>106229</v>
+        <v>80488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781857</v>
+        <v>781918</v>
       </c>
       <c r="R10" t="n">
-        <v>7295534</v>
+        <v>7295526</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1551,12 +1586,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134178476</v>
+        <v>127775000</v>
       </c>
       <c r="B11" t="n">
-        <v>106309</v>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,53 +1639,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långstrandberget, Nb</t>
+          <t>Maran/Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782015</v>
+        <v>781856</v>
       </c>
       <c r="R11" t="n">
-        <v>7295517</v>
+        <v>7295530</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1664,22 +1693,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:44</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:44</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,29 +1707,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134178477</v>
+        <v>127775001</v>
       </c>
       <c r="B12" t="n">
-        <v>106309</v>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1718,53 +1736,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långstrandberget, Nb</t>
+          <t>Maran/Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>782007</v>
+        <v>781881</v>
       </c>
       <c r="R12" t="n">
-        <v>7295501</v>
+        <v>7295532</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1788,22 +1790,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:57</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:57</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,29 +1804,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134178480</v>
+        <v>134178478</v>
       </c>
       <c r="B13" t="n">
-        <v>106309</v>
+        <v>80493</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,53 +1833,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långstrandberget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781874</v>
+        <v>781853</v>
       </c>
       <c r="R13" t="n">
-        <v>7295524</v>
+        <v>7295531</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1917,7 +1892,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1927,7 +1902,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1936,7 +1911,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1955,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127775003</v>
+        <v>135266975</v>
       </c>
       <c r="B14" t="n">
-        <v>97983</v>
+        <v>80493</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1966,37 +1940,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781828</v>
+        <v>781996</v>
       </c>
       <c r="R14" t="n">
-        <v>7295541</v>
+        <v>7295563</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2020,12 +1994,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2052,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134178474</v>
+        <v>135266985</v>
       </c>
       <c r="B15" t="n">
-        <v>99217</v>
+        <v>80493</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,50 +2047,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långstrandberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781969</v>
+        <v>781918</v>
       </c>
       <c r="R15" t="n">
-        <v>7295552</v>
+        <v>7295526</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2138,7 +2106,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2148,7 +2116,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2157,22 +2125,1582 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135266988</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långstandberget  A 24615-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>781857</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7295533</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stuplav på äldre sälg</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127775015</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Maran/Täxtberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>781858</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7295536</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135266976</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långstandberget  A 24615-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>781978</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7295578</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135266981</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långstandberget  A 24615-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>781962</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7295495</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Flera ringhack, färska på äldre gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134178475</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57165</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>781987</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7295546</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flög</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Linda-Marie Grahn</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Linda-Marie Grahn</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127774997</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Maran/Täxtberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>781857</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7295534</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134178476</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>782015</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7295517</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134178477</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>782007</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7295501</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134178480</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>781874</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7295524</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135266978</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långstandberget  A 24615-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>781973</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7295527</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I knopp</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127775003</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Maran/Täxtberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>781828</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7295541</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134178474</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>781969</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7295552</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135266979</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Långstandberget  A 24615-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>782006</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7295530</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135266992</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Långstandberget  A 24615-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>781855</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7295550</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24615-2026 artfynd.xlsx
+++ b/artfynd/A 24615-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266989</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266986</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775009</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266990</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775004</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178479</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266974</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266983</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266984</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775000</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1819,6 +1874,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775001</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178478</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2033,6 +2098,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266975</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,6 +2210,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266985</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2252,6 +2327,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266988</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2349,6 +2429,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775015</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2461,6 +2546,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266976</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2573,6 +2663,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266981</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2685,6 +2780,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178475</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2782,6 +2882,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774997</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2906,6 +3011,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178476</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3030,6 +3140,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178477</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3154,6 +3269,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178480</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3266,6 +3386,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266978</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3363,6 +3488,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775003</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3487,6 +3617,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178474</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3594,6 +3729,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266979</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3701,8 +3841,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266992</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24615-2026 artfynd.xlsx
+++ b/artfynd/A 24615-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135266989</v>
       </c>
       <c r="B2" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135266986</v>
       </c>
       <c r="B3" t="n">
-        <v>97308</v>
+        <v>97352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135266990</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>135266974</v>
       </c>
       <c r="B8" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>135266983</v>
       </c>
       <c r="B9" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135266984</v>
       </c>
       <c r="B10" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>135266975</v>
       </c>
       <c r="B14" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135266985</v>
       </c>
       <c r="B15" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>135266988</v>
       </c>
       <c r="B16" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>135266976</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>135266981</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>134178475</v>
       </c>
       <c r="B20" t="n">
-        <v>57165</v>
+        <v>57170</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>135266978</v>
       </c>
       <c r="B25" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>135266979</v>
       </c>
       <c r="B28" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>135266992</v>
       </c>
       <c r="B29" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2026 artfynd.xlsx
+++ b/artfynd/A 24615-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135266989</v>
       </c>
       <c r="B2" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135266986</v>
       </c>
       <c r="B3" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135266990</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>135266974</v>
       </c>
       <c r="B8" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>135266983</v>
       </c>
       <c r="B9" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135266984</v>
       </c>
       <c r="B10" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>135266975</v>
       </c>
       <c r="B14" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135266985</v>
       </c>
       <c r="B15" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>135266988</v>
       </c>
       <c r="B16" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>135266978</v>
       </c>
       <c r="B25" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>135266979</v>
       </c>
       <c r="B28" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>135266992</v>
       </c>
       <c r="B29" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24615-2026 artfynd.xlsx
+++ b/artfynd/A 24615-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127775009</v>
+        <v>135266989</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781837</v>
+        <v>781856</v>
       </c>
       <c r="R2" t="n">
-        <v>7295531</v>
+        <v>7295511</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre gran med grenar hängande längs  stan, delvis grånade grenar med lav.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,54 +791,54 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127775009</t>
+          <t>https://artportalen.se/Sighting/135266989</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127775004</v>
+        <v>135266986</v>
       </c>
       <c r="B3" t="n">
-        <v>80432</v>
+        <v>97384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781933</v>
+        <v>781866</v>
       </c>
       <c r="R3" t="n">
-        <v>7295515</v>
+        <v>7295532</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,54 +903,54 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127775004</t>
+          <t>https://artportalen.se/Sighting/135266986</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134178479</v>
+        <v>127775009</v>
       </c>
       <c r="B4" t="n">
-        <v>80488</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långstrandberget, Nb</t>
+          <t>Maran/Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781851</v>
+        <v>781837</v>
       </c>
       <c r="R4" t="n">
-        <v>7295532</v>
+        <v>7295531</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,22 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:41</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,65 +994,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134178479</t>
+          <t>https://artportalen.se/Sighting/127775009</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127775000</v>
+        <v>135266990</v>
       </c>
       <c r="B5" t="n">
-        <v>80461</v>
+        <v>79441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781856</v>
+        <v>781844</v>
       </c>
       <c r="R5" t="n">
-        <v>7295530</v>
+        <v>7295502</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,12 +1076,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,38 +1117,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127775000</t>
+          <t>https://artportalen.se/Sighting/135266990</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127775001</v>
+        <v>127775004</v>
       </c>
       <c r="B6" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781881</v>
+        <v>781933</v>
       </c>
       <c r="R6" t="n">
-        <v>7295532</v>
+        <v>7295515</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,38 +1219,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127775001</t>
+          <t>https://artportalen.se/Sighting/127775004</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134178478</v>
+        <v>134178479</v>
       </c>
       <c r="B7" t="n">
-        <v>80493</v>
+        <v>80488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,13 +1260,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781853</v>
+        <v>781851</v>
       </c>
       <c r="R7" t="n">
-        <v>7295531</v>
+        <v>7295532</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,54 +1331,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134178478</t>
+          <t>https://artportalen.se/Sighting/134178479</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127775015</v>
+        <v>135266974</v>
       </c>
       <c r="B8" t="n">
-        <v>80467</v>
+        <v>80556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781858</v>
+        <v>781996</v>
       </c>
       <c r="R8" t="n">
-        <v>7295536</v>
+        <v>7295563</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,12 +1402,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,54 +1443,54 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127775015</t>
+          <t>https://artportalen.se/Sighting/135266974</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127774997</v>
+        <v>135266983</v>
       </c>
       <c r="B9" t="n">
-        <v>106229</v>
+        <v>80556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781857</v>
+        <v>781931</v>
       </c>
       <c r="R9" t="n">
-        <v>7295534</v>
+        <v>7295507</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,12 +1514,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,67 +1560,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127774997</t>
+          <t>https://artportalen.se/Sighting/135266983</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134178476</v>
+        <v>135266984</v>
       </c>
       <c r="B10" t="n">
-        <v>106309</v>
+        <v>80556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långstrandberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>782015</v>
+        <v>781918</v>
       </c>
       <c r="R10" t="n">
-        <v>7295517</v>
+        <v>7295526</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1602,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1612,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1621,34 +1655,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134178476</t>
+          <t>https://artportalen.se/Sighting/135266984</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134178477</v>
+        <v>127775000</v>
       </c>
       <c r="B11" t="n">
-        <v>106309</v>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,53 +1689,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långstrandberget, Nb</t>
+          <t>Maran/Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>782007</v>
+        <v>781856</v>
       </c>
       <c r="R11" t="n">
-        <v>7295501</v>
+        <v>7295530</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1726,22 +1743,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:57</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:57</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,34 +1757,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134178477</t>
+          <t>https://artportalen.se/Sighting/127775000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134178480</v>
+        <v>127775001</v>
       </c>
       <c r="B12" t="n">
-        <v>106309</v>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,53 +1791,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långstrandberget, Nb</t>
+          <t>Maran/Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781874</v>
+        <v>781881</v>
       </c>
       <c r="R12" t="n">
-        <v>7295524</v>
+        <v>7295532</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,22 +1845,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:55</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:55</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1879,34 +1859,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134178480</t>
+          <t>https://artportalen.se/Sighting/127775001</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127775003</v>
+        <v>134178478</v>
       </c>
       <c r="B13" t="n">
-        <v>97983</v>
+        <v>80493</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,37 +1893,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Maran/Täxtberget, Nb</t>
+          <t>Långstrandberget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781828</v>
+        <v>781853</v>
       </c>
       <c r="R13" t="n">
-        <v>7295541</v>
+        <v>7295531</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,12 +1947,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,27 +1977,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127775003</t>
+          <t>https://artportalen.se/Sighting/134178478</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134178474</v>
+        <v>135266975</v>
       </c>
       <c r="B14" t="n">
-        <v>99217</v>
+        <v>80561</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,53 +2005,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långstrandberget, Nb</t>
+          <t>Långstandberget  A 24615-2026, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781969</v>
+        <v>781996</v>
       </c>
       <c r="R14" t="n">
-        <v>7295552</v>
+        <v>7295563</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2091,7 +2064,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2101,7 +2074,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,25 +2083,1767 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135266975</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135266985</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långstandberget  A 24615-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>781918</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7295526</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266985</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135266988</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långstandberget  A 24615-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>781857</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7295533</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stuplav på äldre sälg</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266988</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127775015</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Maran/Täxtberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>781858</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7295536</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775015</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135266976</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långstandberget  A 24615-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>781978</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7295578</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266976</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135266981</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långstandberget  A 24615-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>781962</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7295495</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Flera ringhack, färska på äldre gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266981</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134178475</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57170</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>781987</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7295546</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flög</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178475</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127774997</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Maran/Täxtberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>781857</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7295534</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774997</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134178476</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>782015</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7295517</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178476</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134178477</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>782007</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7295501</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178477</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134178480</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>781874</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7295524</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134178480</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135266978</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106396</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långstandberget  A 24615-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>781973</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7295527</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I knopp</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266978</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127775003</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Maran/Täxtberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>781828</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7295541</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775003</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134178474</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Långstrandberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>781969</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7295552</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134178474</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135266979</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Långstandberget  A 24615-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>782006</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7295530</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266979</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135266992</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Långstandberget  A 24615-2026, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>781855</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7295550</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135266992</t>
         </is>
       </c>
     </row>
@@ -2147,6 +3862,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24615-2026 artfynd.xlsx
+++ b/artfynd/A 24615-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>135266986</v>
       </c>
       <c r="B3" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>135266978</v>
       </c>
       <c r="B25" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>135266979</v>
       </c>
       <c r="B28" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>135266992</v>
       </c>
       <c r="B29" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
